--- a/data/trans_orig/IP1008-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP1008-Habitat-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4428</t>
+          <t>4455</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3219</t>
+          <t>3400</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4898</t>
+          <t>4418</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>134298</t>
+          <t>134271</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>149858</t>
+          <t>149677</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>286905</t>
+          <t>287385</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>643</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6287</t>
+          <t>6174</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7545</t>
+          <t>7515</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2682</t>
+          <t>2725</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11248</t>
+          <t>10607</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>188876</t>
+          <t>188989</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>194511</t>
+          <t>194520</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>204597</t>
+          <t>204627</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>396057</t>
+          <t>396698</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>404623</t>
+          <t>404580</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,33%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1184</t>
+          <t>1183</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7671</t>
+          <t>7365</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2124,77 +2124,77 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>1378</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>8198</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
           <t>1,13%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>4101</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>9021</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>7321</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>3992</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>12893</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,28%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>7321</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>3760</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>12663</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>673350</t>
+          <t>673656</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>679837</t>
+          <t>679838</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,82 +2232,82 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
+          <t>98,92%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,83%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>1080</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>718599</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>714502</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>721322</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>99,43%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
           <t>98,87%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>99,83%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>718599</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>713679</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>720682</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,43%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>98,75%</t>
-        </is>
-      </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
+          <t>99,81%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>2093</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>1396400</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>1390828</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>1399729</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>99,48%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>99,08%</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
           <t>99,72%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>2093</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>1396400</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>1391058</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>1399961</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>99,48%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>99,1%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>99,73%</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3669</t>
+          <t>3010</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>645</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5419</t>
+          <t>5456</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>728</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6852</t>
+          <t>7326</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>132722</t>
+          <t>133381</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>147679</t>
+          <t>147642</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>152449</t>
+          <t>152453</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>282637</t>
+          <t>282163</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>288801</t>
+          <t>288761</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,75%</t>
         </is>
       </c>
     </row>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4741</t>
+          <t>4762</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3746</t>
+          <t>3905</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>646</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5384</t>
+          <t>6063</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3135,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>200657</t>
+          <t>200636</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>218231</t>
+          <t>218072</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>421992</t>
+          <t>421313</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>426729</t>
+          <t>426730</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3095</t>
+          <t>2935</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3347</t>
+          <t>3074</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3752</t>
+          <t>4360</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -3478,7 +3478,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>151744</t>
+          <t>151904</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>162638</t>
+          <t>162911</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>317072</t>
+          <t>316464</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3920</t>
+          <t>3958</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3728,7 +3728,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3931</t>
+          <t>4185</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>206380</t>
+          <t>206342</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>413451</t>
+          <t>413197</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1355</t>
+          <t>1358</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7909</t>
+          <t>8233</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>1256</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7323</t>
+          <t>7159</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3337</t>
+          <t>3368</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12194</t>
+          <t>11708</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>699019</t>
+          <t>698695</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>705573</t>
+          <t>705570</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>740819</t>
+          <t>740983</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>746861</t>
+          <t>746886</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1442876</t>
+          <t>1443362</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1451733</t>
+          <t>1451702</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3401</t>
+          <t>3385</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2951</t>
+          <t>3633</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4923</t>
+          <t>4895</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -4739,7 +4739,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>130306</t>
+          <t>130322</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4754,7 +4754,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>145125</t>
+          <t>144443</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>276860</t>
+          <t>276888</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4969,12 +4969,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>624</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5876</t>
+          <t>6346</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>673</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6277</t>
+          <t>6185</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>201371</t>
+          <t>200901</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>206625</t>
+          <t>206623</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>425329</t>
+          <t>425421</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>430989</t>
+          <t>430933</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,84%</t>
         </is>
       </c>
     </row>
@@ -5317,7 +5317,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3522</t>
+          <t>3478</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5332,7 +5332,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3408</t>
+          <t>4227</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5387,7 +5387,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4566</t>
+          <t>4769</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>152475</t>
+          <t>152519</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -5440,7 +5440,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -5460,7 +5460,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>163265</t>
+          <t>162446</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -5495,7 +5495,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>318104</t>
+          <t>317901</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -5510,7 +5510,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5655,54 +5655,54 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>637</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>6381</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,12%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,31%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,08%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>636</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6564</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>2806</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,31%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,16%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>636</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4264</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -5710,7 +5710,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>781</t>
+          <t>639</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7166</t>
+          <t>7510</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -5768,12 +5768,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>200856</t>
+          <t>201039</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>206784</t>
+          <t>206783</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5783,7 +5783,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>201472</t>
+          <t>202930</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -5818,7 +5818,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>405990</t>
+          <t>405646</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>412375</t>
+          <t>412517</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,85%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2847</t>
+          <t>2826</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11565</t>
+          <t>11751</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>587</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5077</t>
+          <t>5421</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4688</t>
+          <t>4209</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13915</t>
+          <t>13786</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>692806</t>
+          <t>692620</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>701524</t>
+          <t>701545</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>739767</t>
+          <t>739423</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>744260</t>
+          <t>744257</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1435300</t>
+          <t>1435429</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1444527</t>
+          <t>1445006</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,71%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP1008-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP1008-Habitat-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -727,102 +727,102 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4269</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2,79%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>737</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4455</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4262</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,53%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,21%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>673</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>3,07%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1410</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3400</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4380</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>2,22%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1410</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4418</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -835,74 +835,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>152404</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>148808</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,56%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>97,21%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>202</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>137989</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>134271</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>134464</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>138726</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>99,47%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>96,79%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>96,93%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>152404</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>149677</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,56%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>97,78%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>427</t>
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>287385</t>
+          <t>287423</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>203</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,72 +1065,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3428</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1364</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7935</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,62%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3,74%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>2483</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>643</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>6174</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>6044</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,27%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,33%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,16%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>3428</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1356</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>7515</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2725</t>
+          <t>2694</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10607</t>
+          <t>10380</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -1178,74 +1178,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>317</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>208714</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>204207</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>210778</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,38%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>96,26%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,36%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>308</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>192680</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>188989</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>194520</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>189119</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>194511</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>98,73%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>96,84%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>96,9%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>99,67%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>317</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>208714</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>204627</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>210786</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,38%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>96,46%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>99,36%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>625</t>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>396698</t>
+          <t>396925</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>404580</t>
+          <t>404611</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,34%</t>
         </is>
       </c>
     </row>
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>312</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1521,47 +1521,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>137817</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1864,47 +1864,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>274</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>209315</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>274</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,72 +2094,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1381</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>8886</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>3220</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1183</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>7365</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>1167</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>7780</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,47%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,17%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>4101</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>1378</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>8198</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3992</t>
+          <t>3899</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12893</t>
+          <t>12960</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2207,74 +2207,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1080</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>718599</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>713814</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>721319</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,43%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>98,77%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,81%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1013</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>677801</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>673656</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>679838</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>673241</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>679854</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,53%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>98,92%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>98,86%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>99,83%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>718599</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>714502</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>721322</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,43%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>98,87%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,81%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>2093</t>
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1390828</t>
+          <t>1390761</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1399729</t>
+          <t>1399822</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1086</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1086</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2501,7 +2501,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>648</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5405</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1,31%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3,53%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>735</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3010</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3711</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,54%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,21%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>645</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5456</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>728</t>
+          <t>687</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7326</t>
+          <t>6988</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -2782,74 +2782,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>151085</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>147693</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>152450</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>98,69%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>96,47%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>99,58%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>184</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>135656</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>133381</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>132680</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>136391</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>99,46%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>97,79%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>97,28%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>151085</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>147642</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>152453</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>98,69%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>96,44%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>99,58%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>390</t>
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>282163</t>
+          <t>282501</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>288761</t>
+          <t>288802</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,76%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>153098</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>153098</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>153098</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>185</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>136391</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>136391</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>136391</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>153098</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>153098</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>153098</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3012,92 +3012,92 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3116</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1349</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4762</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4562</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,66%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,32%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>2,22%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>647</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3905</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>1,76%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1997</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>646</t>
-        </is>
-      </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6063</t>
+          <t>5426</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -3125,74 +3125,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>221330</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>218861</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>221977</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,71%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>98,6%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>315</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>204049</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>200636</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>200836</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>205398</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,34%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>97,68%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>97,78%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>320</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>221330</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>218072</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>221977</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,71%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>98,24%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>635</t>
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>421313</t>
+          <t>421950</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>426730</t>
+          <t>426729</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>221977</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>221977</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>221977</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>317</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>205398</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>205398</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>205398</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>321</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>221977</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>221977</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>221977</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3360,102 +3360,102 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2466</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>627</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2935</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3791</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,41%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,9%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>607</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>2,45%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3074</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>4717</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>1,85%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1234</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>4360</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -3468,74 +3468,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>165378</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>163519</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>165985</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,63%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>98,51%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>240</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>154212</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>151904</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>151048</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>154839</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>99,59%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>98,1%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>97,55%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>165378</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>162911</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>165985</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,63%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>98,15%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>494</t>
@@ -3548,7 +3548,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>316464</t>
+          <t>316107</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>165985</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>165985</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>165985</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>154839</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>154839</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>154839</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>165985</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>165985</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>165985</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3698,107 +3698,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>787</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3958</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3543</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,37%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1,88%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>1,68%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>787</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>4483</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>787</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>4185</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -3811,74 +3811,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>207082</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>274</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>209513</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>206342</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>206757</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>210300</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,63%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>98,12%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>98,32%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>207082</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>555</t>
@@ -3891,7 +3891,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>413197</t>
+          <t>412899</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -3924,57 +3924,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>207082</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>207082</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>207082</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>275</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>210300</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>210300</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>210300</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>207082</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>207082</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>207082</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4046,67 +4046,67 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>3267</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1282</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>7240</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
           <t>3498</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1358</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>8233</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>1360</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>8640</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,49%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,19%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>3267</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>1256</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>7159</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3368</t>
+          <t>3401</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11708</t>
+          <t>12177</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -4154,74 +4154,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1061</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>744875</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>740902</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>746860</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,56%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>99,03%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,83%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1013</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>703430</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>698695</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>705570</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>698288</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>705568</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,51%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>98,84%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>98,78%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>99,81%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1061</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>744875</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>740983</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>746886</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,56%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>99,04%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,83%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>2074</t>
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1443362</t>
+          <t>1442893</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1451702</t>
+          <t>1451669</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4267,57 +4267,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1066</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4448,7 +4448,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4621,102 +4621,102 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>725</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3635</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2,45%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>675</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3385</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3628</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,5%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,53%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>725</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>2,71%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1400</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3633</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4711</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>2,45%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1400</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4895</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -4729,74 +4729,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>147351</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>144441</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,51%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>97,55%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>133032</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>130322</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>130079</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>133707</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>99,5%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>97,47%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>97,29%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>147351</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>144443</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,51%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>97,55%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>380</t>
@@ -4809,7 +4809,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>276888</t>
+          <t>277072</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4842,57 +4842,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4959,72 +4959,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>2527</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>624</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>6346</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>6325</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,22%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,06%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>622</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6185</t>
+          <t>6351</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -5072,72 +5072,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>330</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>204720</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>200901</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>206623</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>200922</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>206577</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>98,78%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>96,94%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,7%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>332</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>425421</t>
+          <t>425255</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>430933</t>
+          <t>430984</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,86%</t>
         </is>
       </c>
     </row>
@@ -5185,57 +5185,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>334</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>207247</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>207247</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>207247</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>332</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5307,102 +5307,102 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>588</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3045</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1,83%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>699</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3478</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3806</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,45%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,23%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>588</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>2,44%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>1287</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4227</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>4016</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>2,54%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1287</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>4769</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -5415,74 +5415,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>166085</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>163628</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,65%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>98,17%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>155298</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>152519</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>152191</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>155997</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>99,55%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>97,77%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>97,56%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>247</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>166085</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>162446</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,65%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>97,46%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>505</t>
@@ -5495,7 +5495,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>317901</t>
+          <t>318654</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -5510,7 +5510,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5528,57 +5528,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>259</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5645,72 +5645,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>636</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3187</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,31%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>2333</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>637</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6381</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>638</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>6337</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,12%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,31%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,08%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>636</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>2806</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>907</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7510</t>
+          <t>7552</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -5758,74 +5758,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>205100</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>202549</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,69%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>98,45%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>278</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>205087</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>201039</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>206783</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>201083</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>206782</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>98,88%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>96,92%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>96,94%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>99,69%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>289</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>205100</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>202930</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,69%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>98,64%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>567</t>
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>405646</t>
+          <t>405604</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>412517</t>
+          <t>412249</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,78%</t>
         </is>
       </c>
     </row>
@@ -5871,57 +5871,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>281</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>207420</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>207420</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>207420</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>290</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5988,74 +5988,74 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1949</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5708</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>6235</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>2826</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>11751</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>2906</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>11767</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,89%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>1,67%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>1949</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>587</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>5421</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>12</t>
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4209</t>
+          <t>4177</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13786</t>
+          <t>13601</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -6101,72 +6101,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1062</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>742895</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>739136</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>744256</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,74%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>99,23%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,92%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1052</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>698136</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>692620</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>701545</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>692604</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>701465</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,11%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>98,33%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>99,6%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1062</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>742895</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>739423</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>744257</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,74%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>99,27%</t>
-        </is>
-      </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,92%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1435429</t>
+          <t>1435614</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1445006</t>
+          <t>1445038</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -6214,57 +6214,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
